--- a/reports/pdf_change_20260729.xlsx
+++ b/reports/pdf_change_20260729.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,141억   ·   현금 124억(3.4%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 2종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,706억   ·   현금 124억(3.4%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -675,7 +675,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-10771632000</v>
+        <v>-10760773500</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>-19</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>-709627200</v>
+        <v>-708911850</v>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,519억   ·   현금 13억(0.4%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,347억   ·   현금 13억(0.4%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -743,7 +743,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,359억   ·   현금 33억(1.6%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,088억   ·   현금 33억(1.6%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -767,7 +767,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,030억   ·   현금 39억(1.8%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 4종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,953억   ·   현금 35억(1.8%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -863,7 +863,7 @@
         <v>238</v>
       </c>
       <c r="C18" s="17" t="n">
-        <v>6042153600</v>
+        <v>5436300800</v>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>-80</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-5236848000</v>
+        <v>-4711744000</v>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>2188170000</v>
+        <v>1968760000</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>-68</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>-2273335200</v>
+        <v>-2045385600</v>
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>225274500</v>
+        <v>202686000</v>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>-7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-4001067000</v>
+        <v>-3599876000</v>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>276381000</v>
+        <v>248668000</v>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 7억(2.6%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 239억   ·   현금 7억(3.0%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1117,11 +1117,11 @@
         <v>-152</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-733552000</v>
+        <v>-628428800</v>
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>2.72%→0.00%</t>
+          <t>2.64%→0.00%</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 468억   ·   현금 4억(0.9%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 454억   ·   현금 4억(0.9%)      당일 2026-07-29  vs  전영업일 2026-07-28      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1234,7 +1234,7 @@
         <v>-7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>-136598000</v>
+        <v>-135356200</v>
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
